--- a/app/database/price_lookup.xlsx
+++ b/app/database/price_lookup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lagarde\Desktop\switch_breakout\app\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC98561B-5CE1-4895-8B6F-8787D89CB072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E9C4D3-8F48-4EAC-B0C1-A6BEC64FA133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0AB0D9DF-B3E7-4017-A4C6-3E5E0CAF587A}"/>
   </bookViews>
@@ -1608,6 +1608,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB88C83B-97CB-4450-8369-BD2131CAD606}">
   <dimension ref="A1:B249"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -2206,7 +2209,7 @@
         <v>69</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>115000</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
@@ -2214,7 +2217,7 @@
         <v>70</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
@@ -2222,7 +2225,7 @@
         <v>71</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>460000</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
@@ -2902,7 +2905,7 @@
         <v>156</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>15538.4683</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">

--- a/app/database/price_lookup.xlsx
+++ b/app/database/price_lookup.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lagarde\Desktop\switch_breakout\app\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E9C4D3-8F48-4EAC-B0C1-A6BEC64FA133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190261DD-545F-4C0E-A092-6C350B7A0BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0AB0D9DF-B3E7-4017-A4C6-3E5E0CAF587A}"/>
   </bookViews>
   <sheets>
     <sheet name="price_lookup.xlsx" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="339">
   <si>
     <t>code</t>
   </si>
@@ -746,6 +759,297 @@
   </si>
   <si>
     <t>7050CX3M-32S</t>
+  </si>
+  <si>
+    <t>CE16804</t>
+  </si>
+  <si>
+    <t>CE16808</t>
+  </si>
+  <si>
+    <t>CE16816</t>
+  </si>
+  <si>
+    <t>CE16800-X4</t>
+  </si>
+  <si>
+    <t>CE16800-X8</t>
+  </si>
+  <si>
+    <t>CE16800-X16</t>
+  </si>
+  <si>
+    <t>CEX-L48YSAJ</t>
+  </si>
+  <si>
+    <t>CEX-L48YSJ</t>
+  </si>
+  <si>
+    <t>CEX-L72YS6CQJ2</t>
+  </si>
+  <si>
+    <t>CEX-L24CQJ</t>
+  </si>
+  <si>
+    <t>CEX-L36CQJ</t>
+  </si>
+  <si>
+    <t>CEX-L48CQJ2</t>
+  </si>
+  <si>
+    <t>CEX-L18DQJ</t>
+  </si>
+  <si>
+    <t>CEX-L36DQ2CQJ2</t>
+  </si>
+  <si>
+    <t>CEX-L40DQJ2</t>
+  </si>
+  <si>
+    <t>CEX-L36LQJ</t>
+  </si>
+  <si>
+    <t>CEL72XSHGA-P</t>
+  </si>
+  <si>
+    <t>CEL72XS-SAN0</t>
+  </si>
+  <si>
+    <t>CE-L48YSAJ</t>
+  </si>
+  <si>
+    <t>CE-L48YSJ</t>
+  </si>
+  <si>
+    <t>CEL24LQFD-G</t>
+  </si>
+  <si>
+    <t>CEL36LQFD-G</t>
+  </si>
+  <si>
+    <t>CEL36LQFD-A</t>
+  </si>
+  <si>
+    <t>CE-L36LQJ</t>
+  </si>
+  <si>
+    <t>CEL48CQHG-P</t>
+  </si>
+  <si>
+    <t>CEL48CQ-SAN</t>
+  </si>
+  <si>
+    <t>CEL18CQFD-G</t>
+  </si>
+  <si>
+    <t>CEL36CQFD-G</t>
+  </si>
+  <si>
+    <t>CEL18CQFD-A</t>
+  </si>
+  <si>
+    <t>CE-L36CQJ</t>
+  </si>
+  <si>
+    <t>CE-L24CQJ</t>
+  </si>
+  <si>
+    <t>CEL36DQHG-P</t>
+  </si>
+  <si>
+    <t>CEL48DQHG-P</t>
+  </si>
+  <si>
+    <t>CEL36DQHG-X</t>
+  </si>
+  <si>
+    <t>XH16800-8</t>
+  </si>
+  <si>
+    <t>XH16800-16</t>
+  </si>
+  <si>
+    <t>XH-L48CQJ2</t>
+  </si>
+  <si>
+    <t>XH-L36DQ2CQJ2</t>
+  </si>
+  <si>
+    <t>XH-L40DQJ2</t>
+  </si>
+  <si>
+    <t>XH9110-24BQ8DQ</t>
+  </si>
+  <si>
+    <t>XH9210-32DQ</t>
+  </si>
+  <si>
+    <t>XH9230-128DQ</t>
+  </si>
+  <si>
+    <t>CE9875-64EO</t>
+  </si>
+  <si>
+    <t>CE9866-128DQ</t>
+  </si>
+  <si>
+    <t>CE9865-4C</t>
+  </si>
+  <si>
+    <t>CE9860-4C-EI</t>
+  </si>
+  <si>
+    <t>CE98-D8DQ-F</t>
+  </si>
+  <si>
+    <t>CE98-D32CQ-F</t>
+  </si>
+  <si>
+    <t>CE9855-32DQ</t>
+  </si>
+  <si>
+    <t>CE8850-64CQ-EI</t>
+  </si>
+  <si>
+    <t>CE8855-32CQ4BQ</t>
+  </si>
+  <si>
+    <t>CE8865-4C</t>
+  </si>
+  <si>
+    <t>CE88-D10CQ-H</t>
+  </si>
+  <si>
+    <t>CE88-D16CQ-H</t>
+  </si>
+  <si>
+    <t>CE88-D24T2CQ-H</t>
+  </si>
+  <si>
+    <t>CE88-D24YS2CQ-H</t>
+  </si>
+  <si>
+    <t>CE88-D8YS4DQ-H</t>
+  </si>
+  <si>
+    <t>CE8875-24BQ8DQ</t>
+  </si>
+  <si>
+    <t>QFX5700</t>
+  </si>
+  <si>
+    <t>QFX5K-FPC-4CD</t>
+  </si>
+  <si>
+    <t>QFX5K-FPC-20Y</t>
+  </si>
+  <si>
+    <t>QFX5K‑FPC‑16C</t>
+  </si>
+  <si>
+    <t>QFX5241-32OD</t>
+  </si>
+  <si>
+    <t>QFX5240-64OD</t>
+  </si>
+  <si>
+    <t>QFX5240-64QD</t>
+  </si>
+  <si>
+    <t>QFX5241-64OD</t>
+  </si>
+  <si>
+    <t>QFX5241-64QD</t>
+  </si>
+  <si>
+    <t>QFX5230-64CD</t>
+  </si>
+  <si>
+    <t>QFX5100-48S</t>
+  </si>
+  <si>
+    <t>QFX5100-48T</t>
+  </si>
+  <si>
+    <t>QFX5100-24Q</t>
+  </si>
+  <si>
+    <t>QFX5100-24Q+</t>
+  </si>
+  <si>
+    <t>QFX5100-24Q-AA</t>
+  </si>
+  <si>
+    <t>QFX5100-24Q-AA+</t>
+  </si>
+  <si>
+    <t>QFX5100-96S</t>
+  </si>
+  <si>
+    <t>QFX5130</t>
+  </si>
+  <si>
+    <t>QFX5120-48Y</t>
+  </si>
+  <si>
+    <t>QFX5120-48YM</t>
+  </si>
+  <si>
+    <t>QFX5120-48T</t>
+  </si>
+  <si>
+    <t>QFX5120-32C</t>
+  </si>
+  <si>
+    <t>QFX5110-48S</t>
+  </si>
+  <si>
+    <t>QFX5110-32Q</t>
+  </si>
+  <si>
+    <t>QFX5220-32CD</t>
+  </si>
+  <si>
+    <t>QFX5220-128C</t>
+  </si>
+  <si>
+    <t>QFX5210</t>
+  </si>
+  <si>
+    <t>QFX5200-32C</t>
+  </si>
+  <si>
+    <t>QFX5200-48Y</t>
+  </si>
+  <si>
+    <t>QFX10008</t>
+  </si>
+  <si>
+    <t>QFX10016</t>
+  </si>
+  <si>
+    <t>QFX10K-12C-DWDM</t>
+  </si>
+  <si>
+    <t>QFX10000-36Q</t>
+  </si>
+  <si>
+    <t>QFX10000-30C</t>
+  </si>
+  <si>
+    <t>QFX10000-30C-M</t>
+  </si>
+  <si>
+    <t>QFX10000-60S-6Q</t>
+  </si>
+  <si>
+    <t>QFX10002-36Q</t>
+  </si>
+  <si>
+    <t>QFX10002-72Q</t>
+  </si>
+  <si>
+    <t>QFX10002-60C</t>
   </si>
 </sst>
 </file>
@@ -1606,10 +1910,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB88C83B-97CB-4450-8369-BD2131CAD606}">
-  <dimension ref="A1:B249"/>
+  <dimension ref="A1:B348"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -3588,6 +3895,782 @@
         <v>9952.0323590000007</v>
       </c>
     </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>242</v>
+      </c>
+      <c r="B251">
+        <v>76890</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>243</v>
+      </c>
+      <c r="B252">
+        <v>157000</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>244</v>
+      </c>
+      <c r="B253">
+        <v>325000</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>245</v>
+      </c>
+      <c r="B254">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>246</v>
+      </c>
+      <c r="B255">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>247</v>
+      </c>
+      <c r="B256">
+        <v>315000</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>248</v>
+      </c>
+      <c r="B257">
+        <v>2011.1035724065014</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>249</v>
+      </c>
+      <c r="B258">
+        <v>2011.1035724065014</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>250</v>
+      </c>
+      <c r="B259">
+        <v>3541.7818153055237</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>251</v>
+      </c>
+      <c r="B260">
+        <v>3541.7818153055237</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>252</v>
+      </c>
+      <c r="B261">
+        <v>5421.4770766137244</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>253</v>
+      </c>
+      <c r="B262">
+        <v>7333.3649625700882</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>254</v>
+      </c>
+      <c r="B263">
+        <v>11225.330105656549</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>255</v>
+      </c>
+      <c r="B264">
+        <v>23581.449601237477</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>256</v>
+      </c>
+      <c r="B265">
+        <v>25961.272862075351</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>257</v>
+      </c>
+      <c r="B266">
+        <v>2071.4793900884119</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>258</v>
+      </c>
+      <c r="B267">
+        <v>3541.7818153055237</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>259</v>
+      </c>
+      <c r="B268">
+        <v>3541.7818153055237</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>260</v>
+      </c>
+      <c r="B269">
+        <v>2011.1035724065014</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>261</v>
+      </c>
+      <c r="B270">
+        <v>1710.5678622644955</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>262</v>
+      </c>
+      <c r="B271">
+        <v>1353.2710608043105</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>263</v>
+      </c>
+      <c r="B272">
+        <v>2071.4793900884119</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>264</v>
+      </c>
+      <c r="B273">
+        <v>2071.4793900884119</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>265</v>
+      </c>
+      <c r="B274">
+        <v>2071.4793900884119</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>266</v>
+      </c>
+      <c r="B275">
+        <v>7333.3649625700882</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>267</v>
+      </c>
+      <c r="B276">
+        <v>7333.3649625700882</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>268</v>
+      </c>
+      <c r="B277">
+        <v>2618.4008323672333</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>269</v>
+      </c>
+      <c r="B278">
+        <v>5421.4770766137244</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>270</v>
+      </c>
+      <c r="B279">
+        <v>2618.4008323672333</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>271</v>
+      </c>
+      <c r="B280">
+        <v>5421.4770766137244</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>272</v>
+      </c>
+      <c r="B281">
+        <v>3541.7818153055237</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>273</v>
+      </c>
+      <c r="B282">
+        <v>23242.381033853711</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>274</v>
+      </c>
+      <c r="B283">
+        <v>31438.823831904345</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>275</v>
+      </c>
+      <c r="B284">
+        <v>23242.381033853711</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>276</v>
+      </c>
+      <c r="B285">
+        <v>305418.39062561002</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>277</v>
+      </c>
+      <c r="B286">
+        <v>665615.68833628006</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>278</v>
+      </c>
+      <c r="B287">
+        <v>7333.3649625700882</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>279</v>
+      </c>
+      <c r="B288">
+        <v>23581.449601237477</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>280</v>
+      </c>
+      <c r="B289">
+        <v>25961.272862075351</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>281</v>
+      </c>
+      <c r="B290">
+        <v>12538.468301304636</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>282</v>
+      </c>
+      <c r="B291">
+        <v>20572.279988956336</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>283</v>
+      </c>
+      <c r="B292">
+        <v>88086.945940697275</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>284</v>
+      </c>
+      <c r="B293">
+        <v>88086.945940697275</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>285</v>
+      </c>
+      <c r="B294">
+        <v>88086.945940697275</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>286</v>
+      </c>
+      <c r="B295">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>287</v>
+      </c>
+      <c r="B296">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>288</v>
+      </c>
+      <c r="B297">
+        <v>4790.7937822827435</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>289</v>
+      </c>
+      <c r="B298">
+        <v>4790.7937822827435</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>290</v>
+      </c>
+      <c r="B299">
+        <v>20572.279988956336</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>291</v>
+      </c>
+      <c r="B300">
+        <v>9919.4815203093494</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>292</v>
+      </c>
+      <c r="B301">
+        <v>6055.6810206513792</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>293</v>
+      </c>
+      <c r="B302">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>294</v>
+      </c>
+      <c r="B303">
+        <v>1412.5375446227545</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>295</v>
+      </c>
+      <c r="B304">
+        <v>2313.8008793470794</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>296</v>
+      </c>
+      <c r="B305">
+        <v>596.52041360524356</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>297</v>
+      </c>
+      <c r="B306">
+        <v>596.52041360524356</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>298</v>
+      </c>
+      <c r="B307">
+        <v>2618.4008323672333</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>299</v>
+      </c>
+      <c r="B308">
+        <v>12538.468301304636</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>300</v>
+      </c>
+      <c r="B310">
+        <v>42525.748222346941</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>301</v>
+      </c>
+      <c r="B311">
+        <v>2313.8008793470794</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>302</v>
+      </c>
+      <c r="B312">
+        <v>682.21066516070891</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>303</v>
+      </c>
+      <c r="B313">
+        <v>2313.8008793470794</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>304</v>
+      </c>
+      <c r="B314">
+        <v>42560.633306353091</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>305</v>
+      </c>
+      <c r="B315">
+        <v>88050.830989411261</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>306</v>
+      </c>
+      <c r="B316">
+        <v>88050.830989411261</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>307</v>
+      </c>
+      <c r="B317">
+        <v>88050.830989411261</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>308</v>
+      </c>
+      <c r="B318">
+        <v>88050.830989411261</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>309</v>
+      </c>
+      <c r="B319">
+        <v>42525.748222346941</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>310</v>
+      </c>
+      <c r="B320">
+        <v>1000.4585987527388</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>311</v>
+      </c>
+      <c r="B321">
+        <v>1000.4585987527388</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>312</v>
+      </c>
+      <c r="B322">
+        <v>1353.2710608043105</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>313</v>
+      </c>
+      <c r="B323">
+        <v>1830.503097572991</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>314</v>
+      </c>
+      <c r="B324">
+        <v>1353.2710608043105</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>315</v>
+      </c>
+      <c r="B325">
+        <v>1830.503097572991</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>316</v>
+      </c>
+      <c r="B326">
+        <v>1830.503097572991</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>317</v>
+      </c>
+      <c r="B327">
+        <v>20538.582561338029</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>318</v>
+      </c>
+      <c r="B328">
+        <v>2924.7011471139235</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>319</v>
+      </c>
+      <c r="B329">
+        <v>2924.7011471139235</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A330" t="s">
+        <v>320</v>
+      </c>
+      <c r="B330">
+        <v>1531.4222168626673</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A331" t="s">
+        <v>321</v>
+      </c>
+      <c r="B331">
+        <v>4790.7937822827435</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A332" t="s">
+        <v>322</v>
+      </c>
+      <c r="B332">
+        <v>1235.1133211217184</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A333" t="s">
+        <v>323</v>
+      </c>
+      <c r="B333">
+        <v>4790.7937822827435</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A334" t="s">
+        <v>324</v>
+      </c>
+      <c r="B334">
+        <v>20572.279988956336</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A335" t="s">
+        <v>325</v>
+      </c>
+      <c r="B335">
+        <v>20572.279988956336</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A336" t="s">
+        <v>326</v>
+      </c>
+      <c r="B336">
+        <v>9919.4815203093494</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A337" t="s">
+        <v>327</v>
+      </c>
+      <c r="B337">
+        <v>4790.7937822827435</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>328</v>
+      </c>
+      <c r="B338">
+        <v>2618.4008323672333</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A339" t="s">
+        <v>329</v>
+      </c>
+      <c r="B339">
+        <v>82281.708201350717</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A340" t="s">
+        <v>330</v>
+      </c>
+      <c r="B340">
+        <v>170366.7327492194</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A341" t="s">
+        <v>331</v>
+      </c>
+      <c r="B341">
+        <v>1710.5678622644955</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>332</v>
+      </c>
+      <c r="B342">
+        <v>2071.4793900884119</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A343" t="s">
+        <v>333</v>
+      </c>
+      <c r="B343">
+        <v>4476.8992139783222</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>334</v>
+      </c>
+      <c r="B344">
+        <v>4476.8992139783222</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A345" t="s">
+        <v>335</v>
+      </c>
+      <c r="B345">
+        <v>1117.4921636297991</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A346" t="s">
+        <v>336</v>
+      </c>
+      <c r="B346">
+        <v>2071.4793900884119</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A347" t="s">
+        <v>337</v>
+      </c>
+      <c r="B347">
+        <v>4289.0599060377281</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A348" t="s">
+        <v>338</v>
+      </c>
+      <c r="B348">
+        <v>9269.5534476095709</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
